--- a/results/job_matches_2026-05-02.xlsx
+++ b/results/job_matches_2026-05-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Cloud Engineer II</t>
+          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Vibrant Emotional Health</t>
+          <t>J&amp;B Medical</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wixom, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ba39b2a6826c32d</t>
+          <t>https://www.indeed.com/viewjob?jk=823e57252a5543a0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Engineer - AI &amp; Data Management</t>
+          <t>Sr Associate Engineer/ Engineer, IT Data</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S3, Azure, Data Factory, Cloud Storage, Hadoop, HDFS, Spark, Scala, Kafka, Informatica PowerCenter</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f98760c842e5085</t>
+          <t>https://www.indeed.com/viewjob?jk=9512ecb083976839</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/ Engineer, IT Data</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9512ecb083976839</t>
+          <t>https://www.indeed.com/viewjob?jk=80278e0d3375f33b</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Senior Data Engineer, Solutions Architecture</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Clearway Energy</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80278e0d3375f33b</t>
+          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
+          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
+          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Solutions Architecture</t>
+          <t>SRE/Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Clearway Energy</t>
+          <t>Sign In Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
+          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SRE/Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Sign In Solutions</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
+          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,14 +1056,14 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1077,11 +1077,11 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
+          <t>https://www.indeed.com/viewjob?jk=8078bc6f1fdb2e7b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8078bc6f1fdb2e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=957c98b575d28f5a</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dev Ops Data Engineer</t>
+          <t>Cloud / DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
+          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Dev Ops Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Junior Cloud Automation Engineer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
+          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Junior Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Matillion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
+          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Matillion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Matillion</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
+          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Matillion</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
         </is>
       </c>
     </row>
@@ -1693,17 +1693,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
+          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
+          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
+          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
+          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
+          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer (On-Site)</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PTI</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
+          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
+          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
+          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Quality Assurance Analyst / ETL Tester</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Briljent</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Snowflake, Informatica PowerCenter, Oracle, SQL Server, PostgreSQL, Data Modeling, Snowflake Schema, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d69b1256484e3a82</t>
+          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
+          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Junior AWS Cloud Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FuelCloud</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
+          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,67 +2386,67 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
+          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Uniphore</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Core Developer, Full Stack</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
+          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Agentic AI-Senior Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VaaridaTech</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, pytest</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=681aad112795edb7</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Work</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e76fea76e5582b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
+          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
+          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>#Software Engineer – Senior Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2617,11 +2617,11 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
+          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
+          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
+          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Junior Cloud Networking Technician</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
+          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Axis Residential</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spokane, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
+          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Dimensional Modeling, ETL</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62599143d69ab642</t>
+          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6718e8631b0d7a54</t>
+          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Automation Engineer, Finance &amp; Accounting</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, PostgreSQL, AKS, Git</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc4b4b5640d9b20</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>#Software Engineer – Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
+          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Professional Services Consultant</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full-Stack Software Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>PTI</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
+          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
+          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,102 +3156,102 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
+          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>FSO LABS - AI Developer Senior - Bay Area</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
+          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
+          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3282,11 +3282,11 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
+          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
+          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Junior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ObjectStream</t>
+          <t>FuelCloud</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
+          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Java Engineer - Search Platform</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88a1a6638b80a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,67 +3471,67 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
+          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>Uniphore</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Dr. Berg Nutritionals</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,67 +3541,67 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Agentic AI-Senior Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>VaaridaTech</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Lambda, SQS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, pytest</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
+          <t>https://www.indeed.com/viewjob?jk=681aad112795edb7</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Core Developer, Full Stack</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
+          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>#Software Engineer – Senior Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
+          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,42 +3681,1302 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
+          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>AI/ML Engineer - Work</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Cengage</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, MLflow, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e76fea76e5582b6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>FirstNet Global</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Napa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Allegion</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Carmel, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=705778934bc0a50c</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Global Servicing Technology</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>American Express</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Junior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Junior Cloud Networking Technician</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Axis Residential</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Spokane, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Multi-Cloud Networking Engineer</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Solution Architect</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Stellantis</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Dimensional Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62599143d69ab642</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer, Applications</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Basis</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6718e8631b0d7a54</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>#Software Engineer – Engineer</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>San Diego, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>AI Automation Engineer, Finance &amp; Accounting</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Cengage</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>IL, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, PostgreSQL, AKS, Git</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6fc4b4b5640d9b20</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Professional Services Consultant</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Ataccama</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Opeeka, Inc.</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Folsom, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Foster City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>MuleSoft QA Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>UniFirst</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Wilmington, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Wells Fargo</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>FSO LABS - AI Developer Senior - Bay Area</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>EY</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Data Engineer - Sr. Consultant level</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>AWS Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Mutual of Omaha</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>ObjectStream</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Senior Java Engineer - Search Platform</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>RDS, Spark, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Maven, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e88a1a6638b80a7a</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Tessera Labs</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
           <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
         </is>
       </c>
-      <c r="B94" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>Bowery Software Inc</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>Remote, US USA</t>
         </is>
       </c>
-      <c r="D94" t="n">
+      <c r="D129" t="n">
         <v>10.4</v>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E129" t="inlineStr">
         <is>
           <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fe3a1e183165a854</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Front-End Developer/Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, Docker, Kubernetes, Git, Python</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a97387b304714a61</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-02.xlsx
+++ b/results/job_matches_2026-05-02.xlsx
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Professional Services Sales Solutions Architect</t>
+          <t>Agentic AI Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>ElementSkill</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Vertex AI, Spark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
+          <t>https://www.indeed.com/viewjob?jk=87dcf7166c991b47</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Professional Services Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
+          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
         </is>
       </c>
     </row>
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
+          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer</t>
+          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
+          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dev Ops Data Engineer</t>
+          <t>Cloud / DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
+          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Dev Ops Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Junior Cloud Automation Engineer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
+          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Junior Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
+          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
         </is>
       </c>
     </row>
@@ -1553,25 +1553,25 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
+          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte Amalie, VI, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>Associate Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Clinical Care Options LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
+          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
+          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
+          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
+          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
+          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
+          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
+          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
+          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
+          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
+          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
+          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
+          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
+          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
+          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
+          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
+          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
+          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
+          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
+          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
+          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
+          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
+          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
+          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
+          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer (On-Site)</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>PTI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,67 +3121,67 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
+          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Full-Stack Software Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>PTI</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
+          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3212,11 +3212,11 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
+          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,14 +3296,14 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3317,11 +3317,11 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
+          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Junior AWS Cloud Engineer</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FuelCloud</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
+          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Junior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>FuelCloud</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
+          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Uniphore</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Dr. Berg Nutritionals</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Agentic AI-Senior Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>VaaridaTech</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, Azure, GCP, Kafka, NoSQL, CI/CD, Docker, pytest</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=681aad112795edb7</t>
+          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Core Developer, Full Stack</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>#Software Engineer – Senior Engineer</t>
+          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Uniphore</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dr. Berg Nutritionals</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
         </is>
       </c>
     </row>
@@ -3723,17 +3723,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
+          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
+          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Core Developer, Full Stack</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Allegion</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705778934bc0a50c</t>
+          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer II, Global Servicing Technology</t>
+          <t>#Software Engineer – Senior Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, Cloud Storage, Hive, Spark, Scala, ETL, CI/CD, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c5c9f5bf8d54b87</t>
+          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Junior Cloud Networking Technician</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
+          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Axis Residential</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Spokane, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Allegion</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62599143d69ab642</t>
+          <t>https://www.indeed.com/viewjob?jk=705778934bc0a50c</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6718e8631b0d7a54</t>
+          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>#Software Engineer – Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
+          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>AI Automation Engineer, Finance &amp; Accounting</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, PostgreSQL, AKS, Git</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc4b4b5640d9b20</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Professional Services Consultant</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
+          <t>Junior Cloud Networking Technician</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,42 +4196,42 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Axis Residential</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Spokane, WA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
+          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
+          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Basis</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,102 +4311,102 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
+          <t>https://www.indeed.com/viewjob?jk=6718e8631b0d7a54</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>FSO LABS - AI Developer Senior - Bay Area</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Kafka, NoSQL, Power BI, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d75a18fe3bc2126</t>
+          <t>https://www.indeed.com/viewjob?jk=62599143d69ab642</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer - Senior - Consulting - Location Open</t>
+          <t>AI Automation Engineer, Finance &amp; Accounting</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EY</t>
+          <t>Cengage</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Data Modeling, ETL, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, PostgreSQL, AKS, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=599253e2d33dc75f</t>
+          <t>https://www.indeed.com/viewjob?jk=6fc4b4b5640d9b20</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>#Software Engineer – Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
+          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Professional Services Consultant</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,42 +4451,42 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
+          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
+          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
         </is>
       </c>
     </row>
@@ -4498,12 +4498,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ObjectStream</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, Spark, PySpark, ETL, dbt, Airflow, Apache Airflow</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06e3854d22cdba89</t>
+          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Java Engineer - Search Platform</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88a1a6638b80a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
+          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
+          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
+          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Senior Java Engineer - Search Platform</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Spark, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
+          <t>https://www.indeed.com/viewjob?jk=e88a1a6638b80a7a</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=983d0a4b6df6a34b</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,14 +4801,14 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e39cfd742ca8ccb7</t>
+          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,14 +4836,14 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d24b9bb7d3f81d1</t>
+          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406f01e6594b2624</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0206f3baae13d0ec</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-02.xlsx
+++ b/results/job_matches_2026-05-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G130"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,87 +713,87 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (C#/.NET &amp; AI)</t>
+          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>WEX Inc.</t>
+          <t>J&amp;B Medical</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Wixom, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c21b258a08bd24</t>
+          <t>https://www.indeed.com/viewjob?jk=823e57252a5543a0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
+          <t>Sr Associate Engineer/ Engineer, IT Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>J&amp;B Medical</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Wixom, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823e57252a5543a0</t>
+          <t>https://www.indeed.com/viewjob?jk=9512ecb083976839</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/ Engineer, IT Data</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9512ecb083976839</t>
+          <t>https://www.indeed.com/viewjob?jk=80278e0d3375f33b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Senior Data Engineer, Solutions Architecture</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Clearway Energy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80278e0d3375f33b</t>
+          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
+          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
+          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Solutions Architecture</t>
+          <t>SRE/Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Clearway Energy</t>
+          <t>Sign In Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
+          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SRE/Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sign In Solutions</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
+          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
+          <t>https://www.indeed.com/viewjob?jk=8078bc6f1fdb2e7b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Agentic AI Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ElementSkill</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Vertex AI, Spark, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8078bc6f1fdb2e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=87dcf7166c991b47</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Full Stack Software Engineer</t>
+          <t>Senior Professional Services Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=957c98b575d28f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Agentic AI Architect</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ElementSkill</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,42 +1151,42 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Vertex AI, Spark, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87dcf7166c991b47</t>
+          <t>https://www.indeed.com/viewjob?jk=957c98b575d28f5a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Professional Services Sales Solutions Architect</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
         </is>
       </c>
     </row>
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
+          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
+          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
+          <t>Cloud / DevOps Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
+          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer</t>
+          <t>Dev Ops Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Dev Ops Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Junior Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
+          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Junior Cloud Automation Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Matillion</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
+          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
         </is>
       </c>
     </row>
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Matillion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Associate Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Clinical Care Options LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Associate Data &amp; Analytics Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Clinical Care Options LLC</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
+          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Charlotte Amalie, VI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
+          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
+          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
+          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
+          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
+          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
+          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
+          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
+          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
+          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
+          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
+          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
+          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
+          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
+          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
+          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
+          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
+          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
+          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
+          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
+          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
+          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
+          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
+          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Full-Stack Software Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>PTI</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
+          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer (On-Site)</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PTI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3212,11 +3212,11 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
+          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Provoke Solutions</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
+          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
         </is>
       </c>
     </row>
@@ -3338,17 +3338,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Security Engineer - Penetration Testing- Cybersecurity</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, Scala, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=f83c998681a5740b</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Security Engineer - Penetration Testing- Cybersecurity</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Costco Wholesale</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
+          <t>AWS, ECS, IAM, RDS, Azure, GCP, Scala, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=4d9379c5df7ca902</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Junior AWS Cloud Engineer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FuelCloud</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
+          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Data Scientist-Data &amp; Personalization Platform (Hybrid)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Rewards Network</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>City of Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, Kafka, Kafka Connect, PostgreSQL, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
+          <t>https://www.indeed.com/viewjob?jk=b4582e40d2734ff3</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Senior Data Scientist-Intelligent Assignment Engine (Hybrid)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Rewards Network</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, Kafka, Kafka Connect, PostgreSQL, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=28f4e0d1d3bbb168</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Data Scientist-Intelligent Assignment Engine (Hybrid)</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Rewards Network</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>City of Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Scala, Kafka, Kafka Connect, PostgreSQL, dbt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
+          <t>https://www.indeed.com/viewjob?jk=e0c5d2be8683ada1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
+          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
+          <t>Junior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Uniphore</t>
+          <t>FuelCloud</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
+          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Dr. Berg Nutritionals</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AI/ML Engineer - Work</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Snowflake, MLflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e76fea76e5582b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
+          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
+          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Core Developer, Full Stack</t>
+          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>Uniphore</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>#Software Engineer – Senior Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Dr. Berg Nutritionals</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
+          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
+          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Core Developer, Full Stack</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
+          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>#Software Engineer – Senior Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
+          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Allegion</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,14 +4031,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705778934bc0a50c</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4048,15 +4048,15 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,14 +4066,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
+          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4083,15 +4083,15 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
+          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Allegion</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Carmel, IN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
+          <t>https://www.indeed.com/viewjob?jk=705778934bc0a50c</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Junior Cloud Networking Technician</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
+          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Axis Residential</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spokane, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6718e8631b0d7a54</t>
+          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Junior Cloud Networking Technician</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62599143d69ab642</t>
+          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AI Automation Engineer, Finance &amp; Accounting</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Cengage</t>
+          <t>Axis Residential</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Spokane, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Oracle, PostgreSQL, AKS, Git</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fc4b4b5640d9b20</t>
+          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>#Software Engineer – Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
+          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Professional Services Consultant</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>Stellantis</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, S3, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Dimensional Modeling, ETL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=62599143d69ab642</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
+          <t>Sr Software Engineer, Applications</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Basis</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,42 +4476,42 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=6718e8631b0d7a54</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>#Software Engineer – Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
+          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Professional Services Consultant</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,49 +4556,49 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Cloud Storage, Scala, CI/CD, Terraform, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f72c641c65b5a61</t>
+          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
+          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
+          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Java Engineer - Search Platform</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Spark, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Maven, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e88a1a6638b80a7a</t>
+          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
+          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Mutual of Omaha</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
+          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
+          <t>Senior Java Engineer - Search Platform</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>RDS, Spark, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Maven, Kubernetes</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
+          <t>https://www.indeed.com/viewjob?jk=e88a1a6638b80a7a</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Southwest Airlines</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
+          <t>https://www.indeed.com/viewjob?jk=042c9624648e5202</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Senior DevSecOps Architect</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Dragonfli Group LLC</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
+          <t>https://www.indeed.com/viewjob?jk=c0e0643fbf1288ad</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
+          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Bowery Software Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3a1e183165a854</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Front-End Developer/Automation Engineer</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,15 +4966,155 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Tessera Labs</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Bowery Software Inc</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe3a1e183165a854</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Front-End Developer/Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
           <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, Docker, Kubernetes, Git, Python</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=a97387b304714a61</t>
         </is>

--- a/results/job_matches_2026-05-02.xlsx
+++ b/results/job_matches_2026-05-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -818,25 +818,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Solutions Architecture</t>
+          <t>Sr. Software Engineer - AI Engineering and Productivity</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Clearway Energy</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
+          <t>https://www.indeed.com/viewjob?jk=678daaae3aea7ce1</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
+          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
+          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SRE/Engineer</t>
+          <t>Senior Data Engineer, Solutions Architecture</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sign In Solutions</t>
+          <t>Clearway Energy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>SRE/Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Sign In Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,14 +1021,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
+          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8078bc6f1fdb2e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Agentic AI Architect</t>
+          <t>Java Compliance &amp; Governance Developer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ElementSkill</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Vertex AI, Spark, Scala, Snowflake, PostgreSQL</t>
+          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87dcf7166c991b47</t>
+          <t>https://www.indeed.com/viewjob?jk=8078bc6f1fdb2e7b</t>
         </is>
       </c>
     </row>
@@ -1133,25 +1133,25 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Full Stack Software Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=957c98b575d28f5a</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
         </is>
       </c>
     </row>
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
+          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
+          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
+          <t>Cloud / DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
+          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer</t>
+          <t>Dev Ops Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Dev Ops Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Junior Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
+          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Junior Cloud Automation Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
+          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
         </is>
       </c>
     </row>
@@ -1518,25 +1518,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Associate Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Clinical Care Options LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Associate Data &amp; Analytics Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Clinical Care Options LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
+          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
         </is>
       </c>
     </row>
@@ -1763,17 +1763,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
+          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
+          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
+          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
+          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
+          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
+          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
+          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
+          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
+          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
+          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
+          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
+          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
+          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
+          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
+          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
+          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
+          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
+          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
+          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
+          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
+          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
+          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
+          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,17 +3111,17 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, GCP, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1e155aced1efdff</t>
+          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
         </is>
       </c>
     </row>
@@ -3233,17 +3233,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Splunk Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Oracle, SQL Server, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
+          <t>https://www.indeed.com/viewjob?jk=02a1448e52c0de82</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer - Microsoft Fabric</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Provoke Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
+          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Provoke Solutions</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
+          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Security Engineer - Penetration Testing- Cybersecurity</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, Scala, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f83c998681a5740b</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Security Engineer - Penetration Testing- Cybersecurity</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Costco Wholesale</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, GCP, Scala, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d9379c5df7ca902</t>
+          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,14 +3436,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3457,11 +3457,11 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Scientist-Data &amp; Personalization Platform (Hybrid)</t>
+          <t>Junior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Rewards Network</t>
+          <t>FuelCloud</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>City of Chicago, IL, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, Kafka, Kafka Connect, PostgreSQL, dbt</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4582e40d2734ff3</t>
+          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Scientist-Intelligent Assignment Engine (Hybrid)</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Rewards Network</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, Kafka, Kafka Connect, PostgreSQL, dbt</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f4e0d1d3bbb168</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Scientist-Intelligent Assignment Engine (Hybrid)</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Rewards Network</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>City of Chicago, IL, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Scala, Kafka, Kafka Connect, PostgreSQL, dbt</t>
+          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0c5d2be8683ada1</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
+          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Junior AWS Cloud Engineer</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FuelCloud</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
+          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Uniphore</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Dr. Berg Nutritionals</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Core Developer, Full Stack</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
+          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>#Software Engineer – Senior Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
+          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Uniphore</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
+          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Dr. Berg Nutritionals</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
+          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
+          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
+          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Core Developer, Full Stack</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
+          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>#Software Engineer – Senior Engineer</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,14 +3996,14 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
+          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4013,15 +4013,15 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,14 +4031,14 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
+          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4052,11 +4052,11 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,14 +4066,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
+          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4083,15 +4083,15 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
+          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Junior Cloud Networking Technician</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Allegion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Carmel, IN, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, CI/CD, Jenkins, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=705778934bc0a50c</t>
+          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Axis Residential</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Spokane, WA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
+          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Multi-Cloud Networking Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
+          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>#Software Engineer – Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Professional Services Consultant</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Junior Cloud Networking Technician</t>
+          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,42 +4336,42 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
+          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Axis Residential</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spokane, WA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Stellantis</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Dimensional Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62599143d69ab642</t>
+          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Applications</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Basis</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,129 +4486,129 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6718e8631b0d7a54</t>
+          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>#Software Engineer – Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
+          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Professional Services Consultant</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,19 +4731,19 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
+          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer (Snowflake, Teradata, DB2)</t>
+          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Mutual of Omaha</t>
+          <t>Bowery Software Inc</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, SQL Server, MongoDB, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,357 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa9d2ce9f1b5528c</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Senior Java Engineer - Search Platform</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>RDS, Spark, Scala, Kafka, Cassandra, NoSQL, CI/CD, Jenkins, Maven, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e88a1a6638b80a7a</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Southwest Airlines</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, IAM, RDS, Scala, SQL Server, CI/CD</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=042c9624648e5202</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Senior DevSecOps Architect</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Dragonfli Group LLC</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, MLOps, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0e0643fbf1288ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Tessera Labs</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Bowery Software Inc</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=fe3a1e183165a854</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Front-End Developer/Automation Engineer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Samsung Electronics</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, MongoDB, Cassandra, Docker, Kubernetes, Git, Python</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a97387b304714a61</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-02.xlsx
+++ b/results/job_matches_2026-05-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,17 +993,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
+          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Java Compliance &amp; Governance Developer</t>
+          <t>Senior Professional Services Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8078bc6f1fdb2e7b</t>
+          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Professional Services Sales Solutions Architect</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
         </is>
       </c>
     </row>
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
+          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
+          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
+          <t>Cloud / DevOps Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
+          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer</t>
+          <t>Dev Ops Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dev Ops Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Junior Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
+          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Junior Cloud Automation Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
+          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Matillion</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
+          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
         </is>
       </c>
     </row>
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Matillion</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Associate Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Clinical Care Options LLC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Associate Data &amp; Analytics Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Clinical Care Options LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
+          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
+          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte Amalie, VI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,59 +1721,59 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
+          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
+          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
+          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
+          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
+          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
+          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
+          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
+          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
+          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
+          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
+          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
+          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
+          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
+          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
+          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
+          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
+          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
+          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
+          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
+          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
+          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Full-Stack Software Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PTI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
+          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer (On-Site)</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PTI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3177,11 +3177,11 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Splunk Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Oracle, SQL Server, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
+          <t>https://www.indeed.com/viewjob?jk=02a1448e52c0de82</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Splunk Engineer</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Oracle, SQL Server, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a1448e52c0de82</t>
+          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Provoke Solutions</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
+          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer - Microsoft Fabric</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Provoke Solutions</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
+          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Junior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FuelCloud</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
+          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Junior AWS Cloud Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FuelCloud</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
+          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Uniphore</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Uniphore</t>
+          <t>Dr. Berg Nutritionals</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Core Developer, Full Stack</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Dr. Berg Nutritionals</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
+          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
+          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Core Developer, Full Stack</t>
+          <t>#Software Engineer – Senior Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
+          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>#Software Engineer – Senior Engineer</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
+          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
+          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
+          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
+          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
+          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
+          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
+          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,14 +4101,14 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Junior Cloud Networking Technician</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
+          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Junior Cloud Networking Technician</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Axis Residential</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Spokane, WA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,24 +4171,24 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
+          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>#Software Engineer – Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Axis Residential</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spokane, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
+          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Multi-Cloud Networking Engineer</t>
+          <t>Professional Services Consultant</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5089f26e49e819d7</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>#Software Engineer – Engineer</t>
+          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,42 +4266,42 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
+          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Professional Services Consultant</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,49 +4311,49 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
+          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
+          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
+          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,24 +4476,24 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
+          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,24 +4511,24 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
+          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
+          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
+          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Bowery Software Inc</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4695,76 +4695,6 @@
         </is>
       </c>
       <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Bowery Software Inc</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fe3a1e183165a854</t>
         </is>

--- a/results/job_matches_2026-05-02.xlsx
+++ b/results/job_matches_2026-05-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G122"/>
+  <dimension ref="A1:G131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -993,7 +993,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>Senior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
+          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
+          <t>https://www.indeed.com/viewjob?jk=abcb767c36c64a35</t>
         </is>
       </c>
     </row>
@@ -1063,25 +1063,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Professional Services Sales Solutions Architect</t>
+          <t>Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
+          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Professional Services Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
+          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
         </is>
       </c>
     </row>
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
+          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer</t>
+          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
+          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Dev Ops Data Engineer</t>
+          <t>Cloud / DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
+          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Dev Ops Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Junior Cloud Automation Engineer</t>
+          <t>Senior SRE (GCP)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1361,24 +1361,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
+          <t>https://www.indeed.com/viewjob?jk=ce0e1c2c1470a743</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
+          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Junior Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Matillion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
+          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Matillion</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Matillion</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,59 +1511,59 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
+          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Matillion</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Associate Data &amp; Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Clinical Care Options LLC</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte Amalie, VI, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Associate Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Clinical Care Options LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
+          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
+          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
+          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
+          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
+          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
+          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
+          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
+          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
+          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
+          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
+          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
+          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
+          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
+          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
+          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
+          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
+          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
+          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
+          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
+          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
+          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
+          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
+          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
+          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer (On-Site)</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PTI</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3177,11 +3177,11 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
+          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Splunk Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Oracle, SQL Server, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a1448e52c0de82</t>
+          <t>https://www.indeed.com/viewjob?jk=63e4780a404c7463</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Full-Stack Software Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PTI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
+          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer - Microsoft Fabric</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Provoke Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
+          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Splunk Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Oracle, SQL Server, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=02a1448e52c0de82</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Senior Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,24 +3391,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
+          <t>https://www.indeed.com/viewjob?jk=005efcc9b62d1e43</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3422,46 +3422,46 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
+          <t>https://www.indeed.com/viewjob?jk=5f244e9018755770</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Junior AWS Cloud Engineer</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FuelCloud</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
+          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Provoke Solutions</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
+          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
+          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
+          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Uniphore</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
+          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Dr. Berg Nutritionals</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
+          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Core Developer, Full Stack</t>
+          <t>Junior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>FuelCloud</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
+          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>#Software Engineer – Senior Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
+          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
+          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Uniphore</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Dr. Berg Nutritionals</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>Core Developer, Full Stack</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
+          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>#Software Engineer – Senior Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
+          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
+          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Junior Cloud Networking Technician</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
+          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Axis Residential</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spokane, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>#Software Engineer – Engineer</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
+          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Professional Services Consultant</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=322cbaa1c83e7b5b</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,42 +4266,42 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
+          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,14 +4381,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
+          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Junior Cloud Networking Technician</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4402,11 +4402,11 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,102 +4416,102 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Axis Residential</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Spokane, WA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
+          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>#Software Engineer – Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
+          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Professional Services Consultant</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,59 +4521,59 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
+          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
+          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
+          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Bowery Software Inc</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,15 +4686,330 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b57504d4cd793d31</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-05-02</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Tessera Labs</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Bowery Software Inc</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
           <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fe3a1e183165a854</t>
         </is>

--- a/results/job_matches_2026-05-02.xlsx
+++ b/results/job_matches_2026-05-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G131"/>
+  <dimension ref="A1:G127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Neomax</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chantilly, VA, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.1</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776692a890b58814</t>
+          <t>https://www.indeed.com/viewjob?jk=3825710140df8183</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Enterprise Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Data Modeling, ETL</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,94 +671,94 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3825710140df8183</t>
+          <t>https://www.indeed.com/viewjob?jk=a9cff16df0771caf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Enterprise Analytics Data Engineer</t>
+          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>J&amp;B Medical</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Wixom, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9cff16df0771caf</t>
+          <t>https://www.indeed.com/viewjob?jk=823e57252a5543a0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
+          <t>Sr Associate Engineer/ Engineer, IT Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J&amp;B Medical</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wixom, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823e57252a5543a0</t>
+          <t>https://www.indeed.com/viewjob?jk=9512ecb083976839</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/ Engineer, IT Data</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9512ecb083976839</t>
+          <t>https://www.indeed.com/viewjob?jk=80278e0d3375f33b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Sr. Software Engineer - AI Engineering and Productivity</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80278e0d3375f33b</t>
+          <t>https://www.indeed.com/viewjob?jk=678daaae3aea7ce1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Engineering and Productivity</t>
+          <t>Senior Data Engineer, Solutions Architecture</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Clearway Energy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678daaae3aea7ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
+          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
+          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Solutions Architecture</t>
+          <t>SRE/Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Clearway Energy</t>
+          <t>Sign In Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
+          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SRE/Engineer</t>
+          <t>Senior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sign In Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
+          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
+          <t>https://www.indeed.com/viewjob?jk=abcb767c36c64a35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (GCP)</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abcb767c36c64a35</t>
+          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Kubernetes Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>Senior Professional Services Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
+          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Professional Services Sales Solutions Architect</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
         </is>
       </c>
     </row>
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
+          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Cloud / DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
+          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer II _ Big Data, GCP _EDAI</t>
+          <t>Dev Ops Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Scala, PostgreSQL, Data Modeling, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d725c4b26e048534</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dev Ops Data Engineer</t>
+          <t>Senior SRE (GCP)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
+          <t>https://www.indeed.com/viewjob?jk=ce0e1c2c1470a743</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior SRE (GCP)</t>
+          <t>Junior Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1361,24 +1361,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce0e1c2c1470a743</t>
+          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
+          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Junior Cloud Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1462,81 +1462,81 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Matillion</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bbbaf8fbe8db68</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Associate Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Matillion</t>
+          <t>Clinical Care Options LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7ffe9dfedc9c5d</t>
+          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
+          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
+          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Associate Data &amp; Analytics Engineer</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Clinical Care Options LLC</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
+          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Charlotte Amalie, VI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
+          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
+          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
+          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,17 +1851,17 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
+          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
+          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
+          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
+          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
+          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
+          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
+          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
+          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
+          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
+          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
+          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
+          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
+          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
+          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
+          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
+          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
+          <t>https://www.indeed.com/viewjob?jk=63e4780a404c7463</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Full-Stack Software Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>PTI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
+          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
+          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3177,11 +3177,11 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
+          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Splunk Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Oracle, SQL Server, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,49 +3226,49 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63e4780a404c7463</t>
+          <t>https://www.indeed.com/viewjob?jk=02a1448e52c0de82</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer (On-Site)</t>
+          <t>Senior Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>PTI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=005efcc9b62d1e43</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3282,28 +3282,28 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=5f244e9018755770</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
+          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Splunk Engineer</t>
+          <t>Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Provoke Solutions</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Oracle, SQL Server, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a1448e52c0de82</t>
+          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Cloud Automation Engineer</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,24 +3391,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=005efcc9b62d1e43</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f244e9018755770</t>
+          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
+          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer - Microsoft Fabric</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Provoke Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,67 +3506,67 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
+          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Junior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FuelCloud</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,19 +3576,19 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3597,11 +3597,11 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
+          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Junior AWS Cloud Engineer</t>
+          <t>Data Engineer - Performance Management</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>FuelCloud</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>Lake Buena Vista, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
+          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Uniphore</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Dr. Berg Nutritionals</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Core Developer, Full Stack</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
+          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>#Software Engineer – Senior Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
+          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Uniphore</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
+          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Dr. Berg Nutritionals</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
+          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
+          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Core Developer, Full Stack</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>#Software Engineer – Senior Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
+          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
+          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,49 +4066,49 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
+          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
+          <t>https://www.indeed.com/viewjob?jk=322cbaa1c83e7b5b</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4118,15 +4118,15 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,14 +4136,14 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
+          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4153,15 +4153,15 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
+          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,14 +4206,14 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=322cbaa1c83e7b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Cloud Networking Technician</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
+          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Axis Residential</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Spokane, WA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
+          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>#Software Engineer – Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>Professional Services Consultant</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Junior Cloud Networking Technician</t>
+          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Opeeka, Inc.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Folsom, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,42 +4406,42 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
+          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Axis Residential</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Spokane, WA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>#Software Engineer – Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Professional Services Consultant</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,59 +4521,59 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
+          <t>https://www.indeed.com/viewjob?jk=b57504d4cd793d31</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
+          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,34 +4651,34 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
+          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b57504d4cd793d31</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,34 +4756,34 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,34 +4791,34 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
+          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Bowery Software Inc</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4870,146 +4870,6 @@
         </is>
       </c>
       <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Tessera Labs</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Bowery Software Inc</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fe3a1e183165a854</t>
         </is>

--- a/results/job_matches_2026-05-02.xlsx
+++ b/results/job_matches_2026-05-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G127"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,60 +608,60 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>IDB Invest - Data Engineer (Sr Officer) Officer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>Inter-American Development Bank</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>20.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3825710140df8183</t>
+          <t>https://www.indeed.com/viewjob?jk=975f0416f1286d47</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Enterprise Analytics Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,94 +671,94 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9cff16df0771caf</t>
+          <t>https://www.indeed.com/viewjob?jk=3825710140df8183</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
+          <t>Enterprise Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J&amp;B Medical</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wixom, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823e57252a5543a0</t>
+          <t>https://www.indeed.com/viewjob?jk=a9cff16df0771caf</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/ Engineer, IT Data</t>
+          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>J&amp;B Medical</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Wixom, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9512ecb083976839</t>
+          <t>https://www.indeed.com/viewjob?jk=823e57252a5543a0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Sr Associate Engineer/ Engineer, IT Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80278e0d3375f33b</t>
+          <t>https://www.indeed.com/viewjob?jk=9512ecb083976839</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Engineering and Productivity</t>
+          <t>Junior Automation Engineer (Cloud)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678daaae3aea7ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=80278e0d3375f33b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Solutions Architecture</t>
+          <t>Sr. Software Engineer - AI Engineering and Productivity</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Clearway Energy</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
+          <t>https://www.indeed.com/viewjob?jk=678daaae3aea7ce1</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
+          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
         </is>
       </c>
     </row>
@@ -898,7 +898,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
+          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SRE/Engineer</t>
+          <t>Senior Data Engineer, Solutions Architecture</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sign In Solutions</t>
+          <t>Clearway Energy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
+          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (GCP)</t>
+          <t>SRE/Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Sign In Solutions</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
+          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abcb767c36c64a35</t>
+          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=abcb767c36c64a35</t>
         </is>
       </c>
     </row>
@@ -1063,25 +1063,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Professional Services Sales Solutions Architect</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
+          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Sr Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Disney Experiences</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
+          <t>https://www.indeed.com/viewjob?jk=7160da80c4aa5c1b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Professional Services Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
+          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dev Ops Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
+          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Cloud / DevOps Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior SRE (GCP)</t>
+          <t>Dev Ops Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce0e1c2c1470a743</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Junior Cloud Automation Engineer</t>
+          <t>Senior SRE (GCP)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1361,24 +1361,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
+          <t>https://www.indeed.com/viewjob?jk=ce0e1c2c1470a743</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
+          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,14 +1441,14 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
+          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1462,38 +1462,38 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
+          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Associate Data &amp; Analytics Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Clinical Care Options LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Associate Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Clinical Care Options LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte Amalie, VI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
+          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
+          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
+          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
+          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
+          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
+          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
+          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
+          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
+          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
+          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
+          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
+          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
+          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
+          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
+          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
+          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
+          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
+          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
+          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
+          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
+          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
+          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
+          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
+          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
+          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63e4780a404c7463</t>
+          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer (On-Site)</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>PTI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>AI Integration Engineer (Java + AI)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3146,42 +3146,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=63e4780a404c7463</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Full-Stack Software Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>PTI</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,59 +3191,59 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
+          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Splunk Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Oracle, SQL Server, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a1448e52c0de82</t>
+          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Cloud Automation Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=005efcc9b62d1e43</t>
+          <t>https://www.indeed.com/viewjob?jk=011200ffdfb2dd05</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f244e9018755770</t>
+          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Splunk Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,34 +3321,34 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
+          <t>AWS, Azure, Google Cloud Platform, Oracle, SQL Server, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
+          <t>https://www.indeed.com/viewjob?jk=02a1448e52c0de82</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer - Microsoft Fabric</t>
+          <t>Senior Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Provoke Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
+          <t>https://www.indeed.com/viewjob?jk=005efcc9b62d1e43</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Senior Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,24 +3391,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=5f244e9018755770</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Provoke Solutions</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
+          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,14 +3506,14 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3527,46 +3527,46 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
+          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Junior AWS Cloud Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FuelCloud</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
+          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
+          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Junior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>FuelCloud</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
+          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Data Engineer - Performance Management</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Lake Buena Vista, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b85eeb0fd5a3a862</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Uniphore</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Dr. Berg Nutritionals</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
+          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Core Developer, Full Stack</t>
+          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>Uniphore</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>#Software Engineer – Senior Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Dr. Berg Nutritionals</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Core Developer, Full Stack</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
+          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>#Software Engineer – Senior Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, PostgreSQL, MySQL, Splunk, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1869e5a8847d426e</t>
+          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
+          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
+          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,42 +4066,42 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
+          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=322cbaa1c83e7b5b</t>
+          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
         </is>
       </c>
     </row>
@@ -4388,52 +4388,52 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SR DBA / DATABASE ARCHITECT (AZURE / MSSQL)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Opeeka, Inc.</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Folsom, CA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, ETL, CI/CD, Azure DevOps, Bitbucket</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d57af04f58fc4f3b</t>
+          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
+          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,14 +4521,14 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
+          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b57504d4cd793d31</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b57504d4cd793d31</t>
+          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,14 +4626,14 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
+          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4651,17 +4651,17 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
+          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,14 +4766,14 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
+          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
+          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Bowery Software Inc</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4835,41 +4835,6 @@
         </is>
       </c>
       <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Bowery Software Inc</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fe3a1e183165a854</t>
         </is>

--- a/results/job_matches_2026-05-02.xlsx
+++ b/results/job_matches_2026-05-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SRE/Engineer</t>
+          <t>Senior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sign In Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Splunk, CI/CD</t>
+          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78107cea029977e8</t>
+          <t>https://www.indeed.com/viewjob?jk=abcb767c36c64a35</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (GCP)</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,17 +1011,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abcb767c36c64a35</t>
+          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
         </is>
       </c>
     </row>
@@ -1063,25 +1063,25 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior Professional Services Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Sr Full Stack Software Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, MySQL, DynamoDB, Splunk, CI/CD</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7160da80c4aa5c1b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Professional Services Sales Solutions Architect</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
+          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Cloud / DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
+          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Dev Ops Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Dev Ops Data Engineer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
+          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Junior Cloud Automation Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior SRE (GCP)</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ce0e1c2c1470a743</t>
+          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Junior Cloud Automation Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1427,73 +1427,73 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Clinical Care Options LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
+          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
+          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Associate Data &amp; Analytics Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Clinical Care Options LLC</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,67 +1651,67 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
+          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte Amalie, VI, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
+          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
+          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
+          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
+          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
+          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
+          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
+          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
+          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
+          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
+          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
+          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
+          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
+          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
+          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
+          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
+          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
+          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
+          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
+          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
+          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>AWS Technical Apprentice / Trainee</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
+          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Full-Stack Software Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>PTI</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
+          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Cloud DevOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,49 +3086,49 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
+          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
+          <t>https://www.indeed.com/viewjob?jk=011200ffdfb2dd05</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Cloud Support Associate</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3142,46 +3142,46 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, Oracle, DynamoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63e4780a404c7463</t>
+          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer (On-Site)</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>PTI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
+          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Provoke Solutions</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,24 +3251,24 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011200ffdfb2dd05</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
+          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Splunk Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,24 +3321,24 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Oracle, SQL Server, MySQL, MongoDB, Splunk, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a1448e52c0de82</t>
+          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Cloud Automation Engineer</t>
+          <t>Senior Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3352,28 +3352,28 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=005efcc9b62d1e43</t>
+          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Cloud Platform Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3387,11 +3387,11 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, DynamoDB, NoSQL</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f244e9018755770</t>
+          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Junior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FuelCloud</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
+          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer - Microsoft Fabric</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Provoke Solutions</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,59 +3541,59 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Uniphore</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dr. Berg Nutritionals</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Core Developer, Full Stack</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
+          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Junior AWS Cloud Engineer</t>
+          <t>#Software Engineer – Senior Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FuelCloud</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
+          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
+          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
+          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Uniphore</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
+          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Dr. Berg Nutritionals</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
+          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Core Developer, Full Stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
+          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>#Software Engineer – Senior Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
+          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Junior Cloud Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
+          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Junior Cloud Networking Technician</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
+          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>#Software Engineer – Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
+          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>Professional Services Consultant</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
+          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,14 +4206,14 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Junior Cloud Engineer</t>
+          <t>AWS Systems Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4227,11 +4227,11 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,102 +4241,102 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
+          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Junior Cloud Networking Technician</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
+          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Axis Residential</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spokane, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Kimball, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7970a51178c2d8ba</t>
+          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>#Software Engineer – Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
+          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Professional Services Consultant</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,14 +4486,14 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
+          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
+          <t>https://www.indeed.com/viewjob?jk=b57504d4cd793d31</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Bowery Software Inc</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,295 +4546,15 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b57504d4cd793d31</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Tessera Labs</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Bowery Software Inc</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=fe3a1e183165a854</t>
         </is>

--- a/results/job_matches_2026-05-02.xlsx
+++ b/results/job_matches_2026-05-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G118"/>
+  <dimension ref="A1:G99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>IDB Invest - Data Engineer (Sr Officer) Officer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Omada Health</t>
+          <t>Inter-American Development Bank</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,77 +591,77 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, S3, SQS, SNS, BigQuery, Hadoop, Spark</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98dbeaca2ef62c98</t>
+          <t>https://www.indeed.com/viewjob?jk=975f0416f1286d47</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IDB Invest - Data Engineer (Sr Officer) Officer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Inter-American Development Bank</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20.8</v>
+        <v>19.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=975f0416f1286d47</t>
+          <t>https://www.indeed.com/viewjob?jk=3825710140df8183</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Enterprise Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Data Modeling, ETL</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,94 +671,94 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3825710140df8183</t>
+          <t>https://www.indeed.com/viewjob?jk=a9cff16df0771caf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Enterprise Analytics Data Engineer</t>
+          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>J&amp;B Medical</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Wixom, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9cff16df0771caf</t>
+          <t>https://www.indeed.com/viewjob?jk=823e57252a5543a0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
+          <t>Sr Associate Engineer/ Engineer, IT Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J&amp;B Medical</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wixom, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823e57252a5543a0</t>
+          <t>https://www.indeed.com/viewjob?jk=9512ecb083976839</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/ Engineer, IT Data</t>
+          <t>Sr. Software Engineer - AI Engineering and Productivity</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9512ecb083976839</t>
+          <t>https://www.indeed.com/viewjob?jk=678daaae3aea7ce1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Junior Automation Engineer (Cloud)</t>
+          <t>Senior Data Engineer, Solutions Architecture</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Clearway Energy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, Scala, Kafka, Splunk</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80278e0d3375f33b</t>
+          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Engineering and Productivity</t>
+          <t>Senior Data Engineer, Solutions Architecture</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Clearway Energy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678daaae3aea7ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
+          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Solutions Architecture</t>
+          <t>Senior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Clearway Energy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
+          <t>https://www.indeed.com/viewjob?jk=abcb767c36c64a35</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Solutions Architecture</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Clearway Energy</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,67 +951,67 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
+          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (GCP)</t>
+          <t>Senior Professional Services Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abcb767c36c64a35</t>
+          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Cloud / DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Kubernetes Engineer</t>
+          <t>Dev Ops Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, IAM, RDS, Azure, Scala, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f09eaf9518abf0e</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Professional Services Sales Solutions Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc5cd30ba1545c61</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1147,68 +1147,68 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, S3, Hadoop, Spark, Scala</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6622c031669892fa</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dev Ops Data Engineer</t>
+          <t>Associate Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Clinical Care Options LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1217,11 +1217,11 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
+          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ff622ef0e6ac90d</t>
+          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Junior Cloud Automation Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Google Cloud Platform, Spark, PySpark</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86ef316bc56e1d98</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Azure, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,137 +1371,137 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=200956ef0d629800</t>
+          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
+          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Associate Data &amp; Analytics Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Clinical Care Options LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
+          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Charlotte Amalie, VI, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
+          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
+          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
+          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
+          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
+          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
+          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
+          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
+          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
+          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
+          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
+          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
+          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
+          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
+          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
+          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
+          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
+          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
+          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Full-Stack Software Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PTI</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,54 +2701,54 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
+          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=011200ffdfb2dd05</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2757,11 +2757,11 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
+          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Provoke Solutions</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
+          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,67 +2841,67 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Junior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>FuelCloud</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
+          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, RDS, Scala, Kafka, MongoDB, DynamoDB</t>
+          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=294c6d2addcb10cf</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>AWS Technical Apprentice / Trainee</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Microchip Technology</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Step Functions, S3, RDS, Databricks</t>
+          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,67 +3016,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2223f947ee98de60</t>
+          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer (On-Site)</t>
+          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PTI</t>
+          <t>Uniphore</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cloud DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dr. Berg Nutritionals</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, NoSQL, Power BI, Tableau, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,67 +3086,67 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222a5b676c08f8f0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Core Developer, Full Stack</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011200ffdfb2dd05</t>
+          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cloud Support Associate</t>
+          <t>#Software Engineer – Senior Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Spark, Snowflake, MLOps, CI/CD, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39dc124339eab650</t>
+          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AWS Systems Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, SQS, SNS, IAM, Spark, PySpark</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,19 +3191,19 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5e7a473ae9d0b96</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer - Microsoft Fabric</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Provoke Solutions</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3212,11 +3212,11 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
+          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Unity Catalog, Delta Live Tables, Google Cloud Platform, Spark, PySpark, Oracle, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c1348f2e47cd5d6</t>
+          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
+          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Cloud Migration Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, API Gateway, ECS, RDS, Google Cloud Platform, Vertex AI, MySQL, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,67 +3366,67 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93321e0d50904658</t>
+          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Junior AWS Cloud Engineer</t>
+          <t>#Software Engineer – Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FuelCloud</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
+          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Professional Services Consultant</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,67 +3541,67 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Uniphore</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
+          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Dr. Berg Nutritionals</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Core Developer, Full Stack</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,102 +3646,102 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
+          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>#Software Engineer – Senior Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
+          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=68f4f33bf88f7f89</t>
+          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>Bowery Software Inc</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,707 +3856,42 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
+          <t>https://www.indeed.com/viewjob?jk=fe3a1e183165a854</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Foodsmart</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Foodsmart</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>West, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Junior Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Event Hubs, Spark, Kafka, Snowflake, Oracle, ETL</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8d85a7cfec698363</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Junior Cloud Networking Technician</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e73f6230be428620</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>#Software Engineer – Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Professional Services Consultant</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Ataccama</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Foster City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>MuleSoft QA Engineer</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>UniFirst</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Wilmington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Data Engineer - Sr. Consultant level</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>AWS Systems Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, Scala, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=119269e5158f89e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Tessera Labs</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=b57504d4cd793d31</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Bowery Software Inc</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3a1e183165a854</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-02.xlsx
+++ b/results/job_matches_2026-05-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G99"/>
+  <dimension ref="A1:G104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>J&amp;B Medical</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Wixom, MI, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823e57252a5543a0</t>
+          <t>https://www.indeed.com/viewjob?jk=8b84e2ec1da33ebd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/ Engineer, IT Data</t>
+          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>J&amp;B Medical</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Wixom, MI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9512ecb083976839</t>
+          <t>https://www.indeed.com/viewjob?jk=823e57252a5543a0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Engineering and Productivity</t>
+          <t>Sr Associate Engineer/ Engineer, IT Data</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678daaae3aea7ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=9512ecb083976839</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Solutions Architecture</t>
+          <t>Sr. Software Engineer - AI Engineering and Productivity</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Clearway Energy</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
+          <t>https://www.indeed.com/viewjob?jk=678daaae3aea7ce1</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
+          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
+          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (GCP)</t>
+          <t>Senior Data Engineer, Solutions Architecture</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Clearway Energy</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abcb767c36c64a35</t>
+          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=abcb767c36c64a35</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Professional Services Sales Solutions Architect</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
+          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer</t>
+          <t>Senior Professional Services Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
+          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dev Ops Data Engineer</t>
+          <t>Cloud / DevOps Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
+          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Dev Ops Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,14 +1126,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1147,11 +1147,11 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
+          <t>https://www.indeed.com/viewjob?jk=31cbdcc23afc2b45</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Associate Data &amp; Analytics Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Clinical Care Options LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Associate Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Clinical Care Options LLC</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte Amalie, VI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
+          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
+          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
+          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
+          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
+          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
+          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
+          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
+          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
+          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
+          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
+          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
+          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
+          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
+          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
+          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
+          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
+          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
+          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
+          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
+          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
+          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
+          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
+          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
+          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer (On-Site)</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PTI</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>Lakewood, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,102 +2701,102 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>CloudOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tyler Technologies</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Yarmouth, ME, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011200ffdfb2dd05</t>
+          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer - Microsoft Fabric</t>
+          <t>Full-Stack Software Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Provoke Solutions</t>
+          <t>PTI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
+          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,77 +2831,77 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=011200ffdfb2dd05</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Provoke Solutions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
+          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Junior AWS Cloud Engineer</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>FuelCloud</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,19 +2911,19 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2932,11 +2932,11 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
+          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Microchip Technology</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, ETL</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77a528b43d8d11a1</t>
+          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
+          <t>Junior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Uniphore</t>
+          <t>FuelCloud</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
+          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Dr. Berg Nutritionals</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Core Developer, Full Stack</t>
+          <t>Cloud Operations Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Cambridge, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
+          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>#Software Engineer – Senior Engineer</t>
+          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Uniphore</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Cloud Service Desk Analyst</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
+          <t>https://www.indeed.com/viewjob?jk=ad7fea46ba593dc3</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
+          <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Dr. Berg Nutritionals</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>Core Developer, Full Stack</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
+          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>#Software Engineer – Senior Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,14 +3331,14 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
+          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3348,15 +3348,15 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,14 +3366,14 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3383,15 +3383,15 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>#Software Engineer – Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
+          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Professional Services Consultant</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
+          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
+          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
+          <t>#Software Engineer – Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
+          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
+          <t>Professional Services Consultant</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Ataccama</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
+          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
+          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>MuleSoft QA Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>UniFirst</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Wilmington, MA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
+          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
+          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,34 +3776,34 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ff483497142df4</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,34 +3811,34 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
+          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>MuleSoft Architect / Developer Remote (Part-Time / Full-Time) – US Client</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Bowery Software Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,34 +3846,34 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Oracle, ETL, Talend, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe3a1e183165a854</t>
+          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,15 +3881,190 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Engineer II- Java</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Software Engineer, Backend</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Tessera Labs</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
           <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b57504d4cd793d31</t>
         </is>

--- a/results/job_matches_2026-05-02.xlsx
+++ b/results/job_matches_2026-05-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Enterprise Analytics Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>Tampa Electric Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, MySQL, Data Modeling, ETL</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3825710140df8183</t>
+          <t>https://www.indeed.com/viewjob?jk=a9cff16df0771caf</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Enterprise Analytics Data Engineer</t>
+          <t>Junior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tampa Electric Company</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Snowflake, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9cff16df0771caf</t>
+          <t>https://www.indeed.com/viewjob?jk=8b84e2ec1da33ebd</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer (GCP)</t>
+          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>J&amp;B Medical</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Wixom, MI, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b84e2ec1da33ebd</t>
+          <t>https://www.indeed.com/viewjob?jk=823e57252a5543a0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
+          <t>Sr Associate Engineer/ Engineer, IT Data</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>J&amp;B Medical</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Wixom, MI, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, SQL Server, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=823e57252a5543a0</t>
+          <t>https://www.indeed.com/viewjob?jk=9512ecb083976839</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/ Engineer, IT Data</t>
+          <t>Sr. Software Engineer - AI Engineering and Productivity</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9512ecb083976839</t>
+          <t>https://www.indeed.com/viewjob?jk=678daaae3aea7ce1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Engineering and Productivity</t>
+          <t>Senior Data Engineer, Solutions Architecture</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Clearway Energy</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678daaae3aea7ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
+          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
         </is>
       </c>
     </row>
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
+          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Solutions Architecture</t>
+          <t>Senior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Clearway Energy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
+          <t>https://www.indeed.com/viewjob?jk=abcb767c36c64a35</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (GCP)</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,42 +941,42 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abcb767c36c64a35</t>
+          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior Professional Services Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Professional Services Sales Solutions Architect</t>
+          <t>Cloud / DevOps Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
+          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer</t>
+          <t>Dev Ops Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Dev Ops Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Topgolf</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
+          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,69 +1116,69 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=31cbdcc23afc2b45</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31cbdcc23afc2b45</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Associate Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Clinical Care Options LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Associate Data &amp; Analytics Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Clinical Care Options LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
+          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
+          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Charlotte Amalie, VI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,59 +1406,59 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
+          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,17 +1466,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
+          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
+          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
+          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
+          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
+          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
+          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
+          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
+          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
+          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
+          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
+          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
+          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
+          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
+          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
+          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
+          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
+          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
+          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
+          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Full-Stack Software Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>PTI</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,67 +2631,67 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=861e821c88461e16</t>
+          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61fe23b5a013d06d</t>
+          <t>https://www.indeed.com/viewjob?jk=011200ffdfb2dd05</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>Provoke Solutions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lakewood, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0590d6bb95b36919</t>
+          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>CloudOps Engineer</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tyler Technologies</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Yarmouth, ME, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, SQL Server, PostgreSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,102 +2736,102 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9c7752d42fa52c7</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer (On-Site)</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PTI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011200ffdfb2dd05</t>
+          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer - Microsoft Fabric</t>
+          <t>Junior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Provoke Solutions</t>
+          <t>FuelCloud</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
+          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Full Stack Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,49 +2911,49 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Uniphore</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
+          <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dr. Berg Nutritionals</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Junior AWS Cloud Engineer</t>
+          <t>Core Developer, Full Stack</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>FuelCloud</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
+          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
+          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>#Software Engineer – Senior Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
+          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cloud Operations Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>MITSUBISHI ELECTRIC ICONICS DIGITAL SOLUTIONS</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cambridge, MA, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, DynamoDB, CI/CD, AWS CodePipeline, CodeBuild, Terraform</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67d1ed48d145a4f1</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Uniphore</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
+          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cloud Service Desk Analyst</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad7fea46ba593dc3</t>
+          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,17 +3216,17 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
+          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
         </is>
       </c>
     </row>
@@ -3238,20 +3238,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dr. Berg Nutritionals</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
+          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Core Developer, Full Stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
+          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>#Software Engineer – Senior Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>#Software Engineer – Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
+          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,137 +3401,137 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
+          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ff483497142df4</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
+          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
+          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
+          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>#Software Engineer – Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Professional Services Consultant</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ataccama</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7e7f81d2e0f0ce3</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
+          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>MuleSoft QA Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>UniFirst</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Wilmington, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,365 +3706,15 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Blob Storage, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6a8b7edc3d29ab01</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Data Engineer - Sr. Consultant level</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afb2f5fe2a396169</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>St. David's HealthCare</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ff483497142df4</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Tessera Labs</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b57504d4cd793d31</t>
         </is>

--- a/results/job_matches_2026-05-02.xlsx
+++ b/results/job_matches_2026-05-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G94"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Associate Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Clinical Care Options LLC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Associate Data &amp; Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Clinical Care Options LLC</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
         </is>
       </c>
     </row>
@@ -2883,17 +2883,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Full Stack Data Engineer</t>
+          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Uniphore</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, NoSQL, ELT, dbt, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c8001067fa855e4</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Uniphore</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
+          <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dr. Berg Nutritionals</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Core Developer, Full Stack</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Dr. Berg Nutritionals</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
+          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
+          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Core Developer, Full Stack</t>
+          <t>#Software Engineer – Senior Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
+          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>#Software Engineer – Senior Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
+          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
+          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
+          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
+          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
+          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>#Software Engineer – Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>#Software Engineer – Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
+          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ff483497142df4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ff483497142df4</t>
+          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
+          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
+          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,14 +3611,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
+          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,50 +3671,15 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b57504d4cd793d31</t>
         </is>

--- a/results/job_matches_2026-05-02.xlsx
+++ b/results/job_matches_2026-05-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/ Engineer, IT Data</t>
+          <t>Sr. Software Engineer - AI Engineering and Productivity</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Spark, Scala, Snowflake, SQL Server, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9512ecb083976839</t>
+          <t>https://www.indeed.com/viewjob?jk=678daaae3aea7ce1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer - AI Engineering and Productivity</t>
+          <t>Senior Data Engineer, Solutions Architecture</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Clearway Energy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=678daaae3aea7ce1</t>
+          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
+          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
+          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Solutions Architecture</t>
+          <t>Senior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Clearway Energy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
+          <t>https://www.indeed.com/viewjob?jk=abcb767c36c64a35</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (GCP)</t>
+          <t>Software Development Engineer III</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
+          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abcb767c36c64a35</t>
+          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Senior Professional Services Sales Solutions Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Professional Services Sales Solutions Architect</t>
+          <t>Cloud / DevOps Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
+          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer</t>
+          <t>Dev Ops Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>innoVet Health, LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
+          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dev Ops Data Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,42 +1046,42 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
+          <t>https://www.indeed.com/viewjob?jk=31cbdcc23afc2b45</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Topgolf</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Databricks, GCP, Scala, Data Modeling</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,14 +1091,14 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bd117f5a8f07cd9</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1112,11 +1112,11 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31cbdcc23afc2b45</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Associate Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Clinical Care Options LLC</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Associate Data &amp; Analytics Engineer</t>
+          <t>Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Clinical Care Options LLC</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Addison, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
+          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
+          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>IT Full Stack Developer, Commercial</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>ConocoPhillips</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Charlotte Amalie, VI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
+          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
+          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
+          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
+          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
+          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
+          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
+          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
+          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
+          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
+          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
+          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
+          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
+          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
+          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
+          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
+          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
+          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
+          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Full-Stack Software Engineer (On-Site)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PTI</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Mesa, AZ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
+          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=011200ffdfb2dd05</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer (On-Site)</t>
+          <t>Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>PTI</t>
+          <t>Provoke Solutions</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
+          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>DevOps/AI Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MITRE</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011200ffdfb2dd05</t>
+          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer - Microsoft Fabric</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Provoke Solutions</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,94 +2701,94 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
+          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
+          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Junior AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>FuelCloud</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Hillsboro, OR, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
+          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Uniphore</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
+          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Junior AWS Cloud Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FuelCloud</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
+          <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Uniphore</t>
+          <t>Dr. Berg Nutritionals</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Core Developer, Full Stack</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
+          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
+          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>#Software Engineer – Senior Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Dr. Berg Nutritionals</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
+          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Core Developer, Full Stack</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>#Software Engineer – Senior Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
+          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
+          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Snowflake/Tableau Developer / Dallas Texas</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>FirstNet Global</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Napa, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,14 +3121,14 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
+          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3142,11 +3142,11 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
+          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
+          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>#Software Engineer – Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,94 +3261,94 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
+          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ff483497142df4</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>#Software Engineer – Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
+          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,34 +3356,34 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, HBase, Spark, Scala, MySQL, NoSQL, Jenkins, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e151f8f8376a065d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,24 +3391,24 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ff483497142df4</t>
+          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
+          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,120 +3566,15 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b57504d4cd793d31</t>
         </is>

--- a/results/job_matches_2026-05-02.xlsx
+++ b/results/job_matches_2026-05-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G90"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,25 +923,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Professional Services Sales Solutions Architect</t>
+          <t>Cloud / DevOps Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Hadoop, HBase, Spark</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aad68ba091ed0805</t>
+          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,77 +976,77 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
+          <t>https://www.indeed.com/viewjob?jk=31cbdcc23afc2b45</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dev Ops Data Engineer</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>innoVet Health, LLC</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Scala, Oracle, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d7bdd0c563a121a</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31cbdcc23afc2b45</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Clinical Care Options LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
+          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Alignment Healthcare</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Orange, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
+          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Associate Data &amp; Analytics Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Clinical Care Options LLC</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Addison, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Hive, Spark, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b74032a04cfaa28</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte Amalie, VI, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
+          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
+          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IT Full Stack Developer, Commercial</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ConocoPhillips</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Kafka, Snowflake, Oracle, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4afc29839d7e8be</t>
+          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
+          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
+          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
+          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
+          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
+          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
+          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
+          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
+          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
+          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
+          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
+          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
+          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
+          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,77 +2376,77 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
+          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=011200ffdfb2dd05</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Provoke Solutions</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
+          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
+          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
         </is>
       </c>
     </row>
@@ -2512,11 +2512,11 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Full-Stack Software Engineer (On-Site)</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PTI</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Mesa, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, DynamoDB, NoSQL, ELT</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=959a027d133a3e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011200ffdfb2dd05</t>
+          <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer - Microsoft Fabric</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Provoke Solutions</t>
+          <t>Dr. Berg Nutritionals</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DevOps/AI Engineer</t>
+          <t>Core Developer, Full Stack</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MITRE</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, MySQL, MongoDB, MLOps, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dd360cfdc686b9a</t>
+          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
+          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,42 +2761,42 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
+          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Junior AWS Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FuelCloud</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Hillsboro, OR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, MySQL, CI/CD, Terraform, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,207 +2806,207 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05b0071381abb003</t>
+          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer — Data Platform &amp; MAI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Uniphore</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ad11f3ec32fe272</t>
+          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Dr. Berg Nutritionals</t>
+          <t>St. David's HealthCare</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
+          <t>https://www.indeed.com/viewjob?jk=b8ff483497142df4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Core Developer, Full Stack</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
+          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>#Software Engineer – Senior Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d197023697dc7b83</t>
+          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
+          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Snowflake/Tableau Developer / Dallas Texas</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FirstNet Global</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Napa, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6515eadf095c7486</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,425 +3156,40 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
+          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Foodsmart</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>West, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>#Software Engineer – Engineer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Azure, SQL Server, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65ee9e3af0d95deb</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>St. David's HealthCare</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ff483497142df4</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Tessera Labs</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b57504d4cd793d31</t>
         </is>

--- a/results/job_matches_2026-05-02.xlsx
+++ b/results/job_matches_2026-05-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,7 +958,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -972,11 +972,11 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Scala, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31cbdcc23afc2b45</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Associate Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>Clinical Care Options LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Associate Data &amp; Analytics Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Clinical Care Options LLC</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
+          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Alignment Healthcare</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Orange, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, Azure, Data Factory, GCP, Hadoop, Hive, HBase, Spark</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,67 +1126,67 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4cf4da858734131</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte Amalie, VI, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
+          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,17 +1221,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
+          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
+          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
+          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
+          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
+          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
+          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
+          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
+          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
+          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
+          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
+          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
+          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
+          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
+          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
+          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
+          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,104 +2306,104 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
+          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
+          <t>https://www.indeed.com/viewjob?jk=011200ffdfb2dd05</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Provoke Solutions</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Applied AI Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Paramount</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,94 +2411,94 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011200ffdfb2dd05</t>
+          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer - Microsoft Fabric</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Provoke Solutions</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
+          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
+          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
+          <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Dr. Berg Nutritionals</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Core Developer, Full Stack</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
+          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
+          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Dr. Berg Nutritionals</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Core Developer, Full Stack</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
+          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,14 +2701,14 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
+          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2718,15 +2718,15 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,14 +2736,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
+          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2753,15 +2753,15 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
+          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,94 +2806,94 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
+          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>St. David's HealthCare</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,24 +2901,24 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Cloud Storage, Scala, SQL Server, ETL, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8ff483497142df4</t>
+          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
+          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineer, Backend</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tessera Labs</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,120 +3076,15 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b57504d4cd793d31</t>
         </is>

--- a/results/job_matches_2026-05-02.xlsx
+++ b/results/job_matches_2026-05-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Solutions Architecture</t>
+          <t>Senior DevOps Engineer (GCP)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Clearway Energy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3112f4731f8647ad</t>
+          <t>https://www.indeed.com/viewjob?jk=abcb767c36c64a35</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Solutions Architecture</t>
+          <t>Cloud / DevOps Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Clearway Energy</t>
+          <t>Toyota North America</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,67 +811,67 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb476f597eb7b458</t>
+          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Solutions Architecture</t>
+          <t>Cloud AI Application Administrator</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Clearway Energy</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d082d61c4f4a5b69</t>
+          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer (GCP)</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Google Cloud Platform, GCP, Kafka, NoSQL, Data Modeling, ETL, Talend, Tableau, Splunk</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abcb767c36c64a35</t>
+          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Development Engineer III</t>
+          <t>Associate Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Clinical Care Options LLC</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, ECS, RDS, Scala, PostgreSQL, DynamoDB</t>
+          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ad2ef58f346a3ce</t>
+          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud / DevOps Engineer</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Toyota North America</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Charlotte Amalie, VI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, CI/CD, Jenkins</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=616b27159c04b0d8</t>
+          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Cloud AI Application Administrator</t>
+          <t>Site AI Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, Azure, Scala, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18ebfd30511cd60d</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Engineer III - PySpark/AWS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Scala, Snowflake, SQL Server, Data Modeling, Star Schema, ETL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d8ec5a3c163d85b</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Associate Data &amp; Analytics Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Clinical Care Options LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Scala, Data Modeling</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13564543da011952</t>
+          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte Amalie, VI, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c97929cd3c8537a6</t>
+          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Site AI Engineer</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Suffolk Construction</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, ECS, IAM, RDS, Azure, Databricks, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5df1f0f4eb4708</t>
+          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer III - PySpark/AWS</t>
+          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,17 +1151,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6714b6afaed3b1</t>
+          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e860fcc4c94d6d4</t>
+          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7067080d6e07c8f3</t>
+          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9725dda41b26951</t>
+          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d1ce4396f502c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aad35591fe3637b</t>
+          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=485d9362fec2efa2</t>
+          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=076dc7d37ecd84b4</t>
+          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=608d211579ba455d</t>
+          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f187af07a1cb6245</t>
+          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a925391d8a6edf40</t>
+          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=109a6a5bacc8621c</t>
+          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6772d28fdf0b189a</t>
+          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58c41e88c1971000</t>
+          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49997c79b23be02f</t>
+          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d98ee98d5bfcf9d</t>
+          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=774f87e665d21c9c</t>
+          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dfc89a8f43bde62f</t>
+          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94aff22e96326642</t>
+          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80bfce4e39830c30</t>
+          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10bd28821350d25a</t>
+          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3e1d44d1e0404b6</t>
+          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6072f6f6f29b5d2</t>
+          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a3b6706f5bd74b0</t>
+          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ee77db334f5ef9</t>
+          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea139063ea80a8f1</t>
+          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5808657aeae8aab</t>
+          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ed3780e0bd82d7</t>
+          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65f20ec94d3f0499</t>
+          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,77 +2166,77 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0047965fc120080</t>
+          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0d2d1377bcdeb6d</t>
+          <t>https://www.indeed.com/viewjob?jk=011200ffdfb2dd05</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>Data Engineer - Microsoft Fabric</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Provoke Solutions</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,49 +2246,49 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23b259a8f7075b74</t>
+          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ConvergeHEALTH - Data Operations Engineer, Expert Services-Innovation_Delivery_Transformation</t>
+          <t>GCP Support Associate</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Step Functions, S3, RDS, Data Modeling, ETL</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a6e81432a843a50</t>
+          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Junior GCP Cloud Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2302,11 +2302,11 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Scala, Snowflake</t>
+          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d636a662e603c9d</t>
+          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=011200ffdfb2dd05</t>
+          <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer - Microsoft Fabric</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Provoke Solutions</t>
+          <t>Dr. Berg Nutritionals</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Unity Catalog, Spark, PySpark, Scala, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b922fcc276be07d</t>
+          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Applied AI Engineer</t>
+          <t>Core Developer, Full Stack</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Paramount</t>
+          <t>RS21: A Data Science and Visualization Company</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, MLOps, MLflow</t>
+          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f086cee5e98c30b6</t>
+          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GCP Support Associate</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>West, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1097e9f29f6e8b0a</t>
+          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Junior GCP Cloud Engineer</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>ECS, IAM, Google Cloud Platform, GCP, Dataflow, Cloud Storage, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08d4cd78d3dbe405</t>
+          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Software Development Engineer in Test (SDET)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,17 +2516,17 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, Kafka, MLOps, MLflow, CI/CD, Jenkins, Docker</t>
+          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=393116d7c03fb80f</t>
+          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
         </is>
       </c>
     </row>
@@ -2538,20 +2538,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dr. Berg Nutritionals</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Blob Storage, BigQuery, Scala, Snowflake, PostgreSQL, dbt, CI/CD</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c3ced295cf725df</t>
+          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Core Developer, Full Stack</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>RS21: A Data Science and Visualization Company</t>
+          <t>Foodsmart</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, Scala, PostgreSQL, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, AKS</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,14 +2596,14 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af1de6fc24a613b9</t>
+          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2617,11 +2617,11 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,102 +2631,102 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ff1351b933e73ff</t>
+          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=547c7125b0b30619</t>
+          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Development Engineer in Test (SDET)</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Scala, ETL, CI/CD, Jenkins, GitHub Actions, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=364f3e4259c47f25</t>
+          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aaeba0c578886154</t>
+          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Engineer II- Java</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c32c34ff06b9605</t>
+          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer, Backend</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Foodsmart</t>
+          <t>Tessera Labs</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>West, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Scala, Snowflake, PostgreSQL, MySQL, Dimensional Modeling, Airflow, Apache Airflow</t>
+          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c0f59a5cadbe7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b221a3fa0ea5bd27</t>
+          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc63a267293974cf</t>
+          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Engineer II- Java</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,190 +2901,15 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
+          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2ffd59dbc79285e</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Engineer II- Java</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, Azure DevOps, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f4a4f897fc13f95</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Software Engineer, Backend</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Tessera Labs</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, Blob Storage, GCP, Cloud Storage, Scala, Kafka, PostgreSQL, MySQL</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dfac418b5cd8c6bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - New York</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2a9368e0faa9912b</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Data Engineering - Data, Lakehouse and AI Data Platform Engineer - Analyst - Dallas</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Goldman Sachs</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=01fbe5367f7e4246</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, Spark, Scala, Snowflake, ETL, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-05-02</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b57504d4cd793d31</t>
         </is>
